--- a/app/reports/SLBT_research.xlsx
+++ b/app/reports/SLBT_research.xlsx
@@ -618,7 +618,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/SLBT_research.xlsx
+++ b/app/reports/SLBT_research.xlsx
@@ -618,7 +618,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.57</v>
+        <v>1.8306</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05293000221252441</v>
       </c>
     </row>
     <row r="6">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>560759765.6050955</v>
+        <v>560759742.1610401</v>
       </c>
     </row>
     <row r="36">
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.57</v>
+        <v>1.8306</v>
       </c>
     </row>
     <row r="38">
@@ -1491,14 +1491,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>880392832</v>
+        <v>1026526784</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-1.18</v>
+        <v>-1.76</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="7">
